--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R376cdb9900214659"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb80ed2d6258484f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfb80ed2d6258484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63868d31a2884e98"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R63868d31a2884e98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R415b4d4f60d74a9c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R415b4d4f60d74a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95bf06ba0a824feb"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R95bf06ba0a824feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc20ff3881b574905"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc20ff3881b574905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49b92b543f724cba"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49b92b543f724cba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R806abf7a58ba42d3"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R806abf7a58ba42d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96c377df5f4f4bbf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96c377df5f4f4bbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R581e3bf03767453b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R581e3bf03767453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b1d36a231da436a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R7b1d36a231da436a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R725597fb5b1c4b74"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R725597fb5b1c4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d4569d4cfa84598"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d4569d4cfa84598"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa5f11bb558f4a3f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfa5f11bb558f4a3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b807bfe0b35442d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5b807bfe0b35442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4865cbc9a3034488"/>
   </x:sheets>
 </x:workbook>
 </file>
